--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-03).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-03).xlsx
@@ -47,7 +47,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +57,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8EEF5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,9 +101,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -721,21 +713,25 @@
         <v>917090876</v>
       </c>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="7" t="n"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Yakkabog' tumani</t>
+        </is>
+      </c>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>25-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Yakkabog' tumani 25-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>General Secondary School No. 25</t>
+          <t>General Secondary School No. 25, Yakkabog District</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Общеобразовательная школа №25</t>
+          <t>Общеобразовательная школа №25 Яккабагского района</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -777,21 +773,25 @@
         <v>997307709</v>
       </c>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Yakkabog' tumani</t>
+        </is>
+      </c>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>43-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Yakkabog' tumani 43-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>General Secondary School No. 43</t>
+          <t>General Secondary School No. 43, Yakkabog District</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Общеобразовательная школа №43</t>
+          <t>Общеобразовательная школа №43 Яккабагского района</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1687,21 +1687,25 @@
       </c>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="7" t="n"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Yakkabog' tumani</t>
+        </is>
+      </c>
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Yakkabog' tumani 81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>General Secondary School No. 81</t>
+          <t>General Secondary School No. 81, Yakkabog District</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Общеобразовательная школа №81</t>
+          <t>Общеобразовательная школа №81 Яккабагского района</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1869,21 +1873,25 @@
       <c r="F25" s="4" t="n">
         <v>880037679</v>
       </c>
-      <c r="G25" s="7" t="n"/>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Yakkabog' tumani</t>
+        </is>
+      </c>
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Yakkabog' tumani 69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>General Secondary School No. 69</t>
+          <t>General Secondary School No. 69, Yakkabog District</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>Общеобразовательная школа №69</t>
+          <t>Общеобразовательная школа №69 Яккабагского района</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2415,21 +2423,25 @@
         <v>997422473</v>
       </c>
       <c r="F34" s="4" t="n"/>
-      <c r="G34" s="7" t="n"/>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Yakkabog' tumani</t>
+        </is>
+      </c>
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Yakkabog' tumani 69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>General Secondary School No. 69</t>
+          <t>General Secondary School No. 69, Yakkabog District</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>Общеобразовательная школа №69</t>
+          <t>Общеобразовательная школа №69 Яккабагского района</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2535,21 +2547,25 @@
       <c r="F36" s="4" t="n">
         <v>912162304</v>
       </c>
-      <c r="G36" s="7" t="n"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Yakkabog' tumani</t>
+        </is>
+      </c>
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>4-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Yakkabog' tumani 4-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>General Secondary School No. 4</t>
+          <t>General Secondary School No. 4, Yakkabog District</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>Общеобразовательная школа №4</t>
+          <t>Общеобразовательная школа №4 Яккабагского района</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-03).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-03).xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,37 +27,15 @@
     </font>
     <font>
       <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="001E3A8A"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF5"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -86,22 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,2118 +435,1933 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A3:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4.5" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="17.5" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="16.5" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="3.14" customWidth="1" min="1" max="1"/>
+    <col width="34.43" customWidth="1" min="2" max="2"/>
+    <col width="17.29" customWidth="1" min="3" max="3"/>
+    <col width="13.43" customWidth="1" min="4" max="4"/>
+    <col width="17.86" customWidth="1" min="5" max="5"/>
+    <col width="22.57" customWidth="1" min="6" max="6"/>
+    <col width="21.71" customWidth="1" min="7" max="7"/>
+    <col width="17.71" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="26.29" customWidth="1" min="10" max="10"/>
+    <col width="13.86" customWidth="1" min="11" max="11"/>
+    <col width="16.43" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Guruh 26-03 (33 nafar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Namuna: Saydalimov Anvarjon Sarvarjon o`g`li | 517******0016 | AC1686958 | 990201527 | Qashqadaryo, Qarshi | 4-mittituman 21/23 | Qarshi shahar 1-maktab | Qarshi City School No. 1 | Школа №1 города Карши | Maktab | AA1775603 | 2008-2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="63" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="47.25" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>F.I.O</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>JSHSHIR</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Pasport seriya raqami</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>2-Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Yashash viloyat+tumani</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>UY manzili</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Uzbek tilida)</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Ingliz tilida)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Avval o`qigan muassasa nomi(Rus tilida)</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Maktab, kollej va HK</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Avval olgan diplom seriya+raqami</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Boshlagan va tugatgan yili</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="n">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Aliqulova Shaxzoda Anvar qizi</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>60301037890018</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>AC1827958</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Surxondaryo viloyati</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Surxondaryo viloyati 6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 6, Surkhandarya Region</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №6 Сурхандарьинской области</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>UM 0440372</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>2009-2020</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Arziqulova Laylo Bahodir qizi</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>60110065720109</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>AD8548125</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="2" t="n">
         <v>940790106</v>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 50-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 50, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №50 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>UM 03264433</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Eshnazarova Dilnoza Rustam qizi</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>60710085730098</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>AE3321050</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="2" t="n">
         <v>917090876</v>
       </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 25-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 25, Yakkabog District</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №25 Яккабагского района</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>UM 03756638</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Fayzullayeva Sarvinoz Sherbobo qizi</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>63003055730053</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>AD1189588</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="2" t="n">
         <v>997307709</v>
       </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 43-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 43, Yakkabog District</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №43 Яккабагского района</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>UM 01926806</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>2012-2023</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Ibragimova Gulnoza Isroil qizi</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>60606085680085</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>AE4115057</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="2" t="n">
         <v>952590625</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="2" t="n">
         <v>991523371</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 21, Kitob District</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №21 Китабского района</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>UM 03728618</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Izzatulloyeva Vazira G'ayratzoda</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>42004975680094</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>AE5671026</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="2" t="n">
         <v>873588797</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="2" t="n">
         <v>886321972</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Kitob agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Kitob Vocational College of Agribusiness</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>Китабский профессиональный колледж агробизнеса</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>K 4174595</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>2013-2016</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Jurayeva Dilnoz G'oibnazarovna</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>40305922560019</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>AD2957442</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="2" t="n">
         <v>999430596</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="2" t="n">
         <v>959399205</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 58-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 58, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №58 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>O'R-SH 1074334</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>1999-2010</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Mansurova Gulasal Musurmon qizi</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>62905085680067</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>AE4483600</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="2" t="n">
         <v>939034744</v>
       </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 20, Kitob District</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №20 Китабского района</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>UM 03728547</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Murtazayeva Kamola Jamoliddin qizi</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>42708915590028</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>AC1458884</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="2" t="n">
         <v>888039193</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="2" t="n">
         <v>887261412</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Specialized School, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>Специализированная школа Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>O'R-SH 0987579</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>1998-2009</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Mustafayeva Madina Ortiq qizi</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>63110085680103</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>AE4846447</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 49-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 49, Kitob District</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №49 Китабского района</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>UM 03729407</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Niyozova Komila Toshpulatovna</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>42405832640057</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>AB9205278</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 21, Kitob District</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №21 Китабского района</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>DB 00222382</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>1989-2000</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Norboboyeva Farangiz Nuriddin qizi</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>62808085590100</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>AE5898909</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="2" t="n">
         <v>970012780</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="2" t="n">
         <v>973157721</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 19, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №19 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>UM 03753862</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="n">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Pardaqulova Farzona Shovkatovna</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>60312085590052</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>AE1336538</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="2" t="n">
         <v>772131924</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="2" t="n">
         <v>919584082</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 61, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №61 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>UM 03755343</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Pardayeva Farangiz Norali qizi</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>60102085590053</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>AE5643897</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="2" t="n">
         <v>876450108</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="2" t="n">
         <v>990427984</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 68-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 68, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №68 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>UM 03755453</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="4" t="n">
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Primova Husnora Shovkat qizi</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>61310015590029</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>AC0443770</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="2" t="n">
         <v>873920025</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="2" t="n">
         <v>873920021</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz texnologiya kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Technology</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>Шахрисабзский технологический профессиональный колледж</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>D 0095067</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="4" t="n">
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Rasulova Husnobod Bekmurod qizi</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>62705055720049</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>AD1615363</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="2" t="n">
         <v>503019503</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="2" t="n">
         <v>997304804</v>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 49-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 49, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №49 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>UM 01891815</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>2012-2023</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="n">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Rayimova Nozliya Laziz qizi</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>62606085590056</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>AE4759683</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="2" t="n">
         <v>919595774</v>
       </c>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 68-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 68, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №68 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>UM 03755475</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Rustamova Charos O'ktam qizi</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>60810085680017</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>AE4730990</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="2" t="n">
         <v>880632608</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="2" t="n">
         <v>973360140</v>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 4-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 4, Kitob District</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №4 Китабского района</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>UM 03728038</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="n">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Salayeva Dilroz Muroulla qizi</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>60408085730030</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>AE3039330</t>
         </is>
       </c>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 81, Yakkabog District</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №81 Яккабагского района</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>UM 03758292</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="4" t="n">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>61007085590081</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>AD7984192</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="2" t="n">
         <v>880001458</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="2" t="n">
         <v>905176163</v>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 7, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №7 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>UM 03751932</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="4" t="n">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>62708095680047</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>AE6071273</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="2" t="n">
         <v>330578323</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="2" t="n">
         <v>334248323</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 38-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 38, Kitob District</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №38 Китабского района</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>UM 03729168</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="4" t="n">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>60307085730074</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>AE2370999</t>
         </is>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="2" t="n">
         <v>885020703</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="2" t="n">
         <v>880037679</v>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 69, Yakkabog District</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №69 Яккабагского района</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>UM 03758004</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="n">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Shukurova Zilola Farxod qizi</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>60610085590150</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>AE1059205</t>
         </is>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="2" t="n">
         <v>704785808</v>
       </c>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-son texnikumi</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Technical School No. 1, Kitob District</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>Техникум №1 Китабского района</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Texnikum</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>PT 0339050</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>2023-2026</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="4" t="n">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Temirova Rushana Sarvarovna</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>60709085590113</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>AD9123776</t>
         </is>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="2" t="n">
         <v>955838858</v>
       </c>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 61, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №61 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>UM 03755349</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="n">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>61709085590015</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>AE3444231</t>
         </is>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="2" t="n">
         <v>971880757</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="2" t="n">
         <v>973810757</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 26, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №26 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>UM 03754061</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="4" t="n">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>60906055720101</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>AD1671106</t>
         </is>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="2" t="n">
         <v>875615296</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="2" t="n">
         <v>772322878</v>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 42-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 42, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №42 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>UM 01891594</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>2012-2023</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="4" t="n">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>62112075680077</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>AD9589389</t>
         </is>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="2" t="n">
         <v>876310721</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="2" t="n">
         <v>875280782</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 12, Kitob District</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №12 Китабского района</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>UM 03273678</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="4" t="n">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>61906085590032</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>AE4240266</t>
         </is>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="2" t="n">
         <v>888659008</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="2" t="n">
         <v>881861712</v>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 26, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №26 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>UM 03754068</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="4" t="n">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>61911085590096</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>AD9786798</t>
         </is>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="2" t="n">
         <v>772254208</v>
       </c>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-son texnikumi</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Technical School No. 1, Kitob District</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>Техникум №1 Китабского района</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Texnikum</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>PT 0025701</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>2023-2026</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="4" t="n">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>60201085720092</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>AE4328716</t>
         </is>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="2" t="n">
         <v>908785105</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="2" t="n">
         <v>916397685</v>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 36, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №36 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>UM 03718337</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="4" t="n">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>62511085730064</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>AE4729924</t>
         </is>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="2" t="n">
         <v>997422473</v>
       </c>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 69, Yakkabog District</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №69 Яккабагского района</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>UM 03758009</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="4" t="n">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Xurramova Lobar Ural qizi</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>62508085680062</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>AE2656510</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="2" t="n">
         <v>881708081</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="2" t="n">
         <v>880410227</v>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 12, Kitob District</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №12 Китабского района</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>UM 03728374</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="4" t="n">
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Xurramova Sabina Yuldosh qizi</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>60803048230011</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>AC3081523</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="2" t="n">
         <v>979602535</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="2" t="n">
         <v>912162304</v>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 4-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 4, Yakkabog District</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №4 Яккабагского района</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>UM 1315230</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>2011-2022</t>
         </is>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-03).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-03).xlsx
@@ -435,22 +435,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:M36"/>
+  <dimension ref="A3:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.14" customWidth="1" min="1" max="1"/>
-    <col width="34.43" customWidth="1" min="2" max="2"/>
-    <col width="17.29" customWidth="1" min="3" max="3"/>
-    <col width="13.43" customWidth="1" min="4" max="4"/>
-    <col width="17.86" customWidth="1" min="5" max="5"/>
-    <col width="22.57" customWidth="1" min="6" max="6"/>
-    <col width="21.71" customWidth="1" min="7" max="7"/>
-    <col width="17.71" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="26.29" customWidth="1" min="10" max="10"/>
-    <col width="13.86" customWidth="1" min="11" max="11"/>
-    <col width="16.43" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34.43" customWidth="1" min="3" max="3"/>
+    <col width="17.29" customWidth="1" min="4" max="4"/>
+    <col width="13.43" customWidth="1" min="5" max="5"/>
+    <col width="17.86" customWidth="1" min="6" max="6"/>
+    <col width="22.57" customWidth="1" min="7" max="7"/>
+    <col width="21.71" customWidth="1" min="8" max="8"/>
+    <col width="17.71" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="26.29" customWidth="1" min="11" max="11"/>
+    <col width="13.86" customWidth="1" min="12" max="12"/>
+    <col width="16.43" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="3" ht="47.25" customHeight="1">
@@ -461,60 +462,65 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
+          <t>Guruhi</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
           <t>F.I.O</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>JSHSHIR</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Pasport seriya raqami</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>2-Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Yashash viloyat+tumani</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>UY manzili</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Uzbek tilida)</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Ingliz tilida)</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Maktab, kollej va HK</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Avval olgan diplom seriya+raqami</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>Boshlagan va tugatgan yili</t>
         </is>
@@ -526,48 +532,53 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>Aliqulova Shaxzoda Anvar qizi</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>60301037890018</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>AC1827958</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Surxondaryo viloyati</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Surxondaryo viloyati 6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 6, Surkhandarya Region</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>UM 0440372</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2009-2020</t>
         </is>
@@ -579,50 +590,55 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>Arziqulova Laylo Bahodir qizi</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>60110065720109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>AD8548125</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>940790106</v>
       </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 50-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 50, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>UM 03264433</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
@@ -634,50 +650,55 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>Eshnazarova Dilnoza Rustam qizi</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>60710085730098</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>AE3321050</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>917090876</v>
       </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 25-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 25, Yakkabog District</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>UM 03756638</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -689,50 +710,55 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>Fayzullayeva Sarvinoz Sherbobo qizi</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>63003055730053</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>AD1189588</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>997307709</v>
       </c>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 43-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 43, Yakkabog District</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t>UM 01926806</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2012-2023</t>
         </is>
@@ -744,52 +770,57 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>Ibragimova Gulnoza Isroil qizi</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>60606085680085</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>AE4115057</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>952590625</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>991523371</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 21, Kitob District</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>UM 03728618</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -801,52 +832,57 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>Izzatulloyeva Vazira G'ayratzoda</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>42004975680094</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>AE5671026</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>873588797</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>886321972</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Kitob agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Kitob Vocational College of Agribusiness</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>K 4174595</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>2013-2016</t>
         </is>
@@ -858,52 +894,57 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>Jurayeva Dilnoz G'oibnazarovna</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>40305922560019</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>AD2957442</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>999430596</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>959399205</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 58-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 58, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>O'R-SH 1074334</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1999-2010</t>
         </is>
@@ -915,50 +956,55 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>Mansurova Gulasal Musurmon qizi</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>62905085680067</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>AE4483600</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>939034744</v>
       </c>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 20, Kitob District</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>UM 03728547</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -970,52 +1016,57 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>Murtazayeva Kamola Jamoliddin qizi</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>42708915590028</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>AC1458884</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>888039193</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>887261412</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Specialized School, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>O'R-SH 0987579</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>1998-2009</t>
         </is>
@@ -1027,48 +1078,53 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>Mustafayeva Madina Ortiq qizi</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>63110085680103</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>AE4846447</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 49-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 49, Kitob District</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
           <t>UM 03729407</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1080,48 +1136,53 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>Niyozova Komila Toshpulatovna</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>42405832640057</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>AB9205278</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 21, Kitob District</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>DB 00222382</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1989-2000</t>
         </is>
@@ -1133,52 +1194,57 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>Norboboyeva Farangiz Nuriddin qizi</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>62808085590100</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>AE5898909</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="F15" s="2" t="n">
         <v>970012780</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="G15" s="2" t="n">
         <v>973157721</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 19, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
           <t>UM 03753862</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1190,52 +1256,57 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>Pardaqulova Farzona Shovkatovna</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>60312085590052</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>AE1336538</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="F16" s="2" t="n">
         <v>772131924</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>919584082</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 61, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t>UM 03755343</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1247,52 +1318,57 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>Pardayeva Farangiz Norali qizi</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>60102085590053</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>AE5643897</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="F17" s="2" t="n">
         <v>876450108</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>990427984</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 68-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 68, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>UM 03755453</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1304,52 +1380,57 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>Primova Husnora Shovkat qizi</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>61310015590029</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>AC0443770</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="F18" s="2" t="n">
         <v>873920025</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>873920021</v>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz texnologiya kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Technology</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>D 0095067</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
@@ -1361,52 +1442,57 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>Rasulova Husnobod Bekmurod qizi</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>62705055720049</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>AD1615363</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="F19" s="2" t="n">
         <v>503019503</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="G19" s="2" t="n">
         <v>997304804</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 49-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 49, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
           <t>UM 01891815</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2012-2023</t>
         </is>
@@ -1418,50 +1504,55 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>Rayimova Nozliya Laziz qizi</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>62606085590056</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>AE4759683</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="F20" s="2" t="n">
         <v>919595774</v>
       </c>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 68-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 68, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
           <t>UM 03755475</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1473,52 +1564,57 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>Rustamova Charos O'ktam qizi</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>60810085680017</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>AE4730990</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="F21" s="2" t="n">
         <v>880632608</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="G21" s="2" t="n">
         <v>973360140</v>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 4-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 4, Kitob District</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
           <t>UM 03728038</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1530,48 +1626,53 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
           <t>Salayeva Dilroz Muroulla qizi</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>60408085730030</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>AE3039330</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 81, Yakkabog District</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t>UM 03758292</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1583,52 +1684,57 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>61007085590081</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>AD7984192</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="F23" s="2" t="n">
         <v>880001458</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>905176163</v>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 7, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
           <t>UM 03751932</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1640,52 +1746,57 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>62708095680047</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>AE6071273</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="F24" s="2" t="n">
         <v>330578323</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>334248323</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 38-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 38, Kitob District</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
           <t>UM 03729168</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1697,52 +1808,57 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
           <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>60307085730074</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>AE2370999</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="F25" s="2" t="n">
         <v>885020703</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>880037679</v>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 69, Yakkabog District</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
           <t>UM 03758004</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1754,50 +1870,55 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
           <t>Shukurova Zilola Farxod qizi</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>60610085590150</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>AE1059205</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="F26" s="2" t="n">
         <v>704785808</v>
       </c>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-son texnikumi</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Technical School No. 1, Kitob District</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Texnikum</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>PT 0339050</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>2023-2026</t>
         </is>
@@ -1809,50 +1930,55 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
           <t>Temirova Rushana Sarvarovna</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>60709085590113</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>AD9123776</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="F27" s="2" t="n">
         <v>955838858</v>
       </c>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 61, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
           <t>UM 03755349</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1864,52 +1990,57 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
           <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>61709085590015</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>AE3444231</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="F28" s="2" t="n">
         <v>971880757</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>973810757</v>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 26, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
           <t>UM 03754061</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1921,54 +2052,57 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>60906055720101</t>
+          <t>Tursunmurodova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>AD1671106</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>875615296</v>
+          <t>61609075680011</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>AD9513015</t>
+        </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>772322878</v>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Shahrisabz shahri 42-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
+        <v>887611310</v>
+      </c>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Kitob tumani</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>General Secondary School No. 42, Shahrisabz City</t>
+          <t>Kitob tumani 25-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Maktab</t>
+          <t>General Secondary School No. 25, Kitob District</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>UM 01891594</t>
+          <t>Maktab</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2012-2023</t>
+          <t>UM 03274052</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2014-2025</t>
         </is>
       </c>
     </row>
@@ -1978,54 +2112,59 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>62112075680077</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>AD9589389</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>876310721</v>
+          <t>60906055720101</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>AD1671106</t>
+        </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>875280782</v>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Qashqadaryo, Kitob tumani</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Kitob tumani 12-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
+        <v>875615296</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>772322878</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>General Secondary School No. 12, Kitob District</t>
+          <t>Shahrisabz shahri 42-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Maktab</t>
+          <t>General Secondary School No. 42, Shahrisabz City</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>UM 03273678</t>
+          <t>Maktab</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2014-2025</t>
+          <t>UM 01891594</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2012-2023</t>
         </is>
       </c>
     </row>
@@ -2035,54 +2174,59 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>61906085590032</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>AE4240266</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>888659008</v>
+          <t>62112075680077</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>AD9589389</t>
+        </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>881861712</v>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani 26-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
+        <v>876310721</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>875280782</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Kitob tumani</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>General Secondary School No. 26, Shahrisabz District</t>
+          <t>Kitob tumani 12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Maktab</t>
+          <t>General Secondary School No. 12, Kitob District</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>UM 03754068</t>
+          <t>Maktab</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2015-2026</t>
+          <t>UM 03273678</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>2014-2025</t>
         </is>
       </c>
     </row>
@@ -2092,52 +2236,59 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>61911085590096</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>AD9786798</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>772254208</v>
-      </c>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Qashqadaryo, Kitob tumani</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Kitob tumani 1-son texnikumi</t>
-        </is>
-      </c>
+          <t>61906085590032</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>AE4240266</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>888659008</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>881861712</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Technical School No. 1, Kitob District</t>
+          <t>Shahrisabz tumani 26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Texnikum</t>
+          <t>General Secondary School No. 26, Shahrisabz District</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>PT 0025701</t>
+          <t>Maktab</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2023-2026</t>
+          <t>UM 03754068</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>2015-2026</t>
         </is>
       </c>
     </row>
@@ -2147,54 +2298,57 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>60201085720092</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>AE4328716</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>908785105</v>
+          <t>61911085590096</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>AD9786798</t>
+        </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>916397685</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Shahrisabz shahri 36-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
+        <v>772254208</v>
+      </c>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Kitob tumani</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>General Secondary School No. 36, Shahrisabz City</t>
+          <t>Kitob tumani 1-son texnikumi</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Maktab</t>
+          <t>Technical School No. 1, Kitob District</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>UM 03718337</t>
+          <t>Texnikum</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2015-2026</t>
+          <t>PT 0025701</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>2023-2026</t>
         </is>
       </c>
     </row>
@@ -2204,50 +2358,57 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>62511085730064</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>AE4729924</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>997422473</v>
-      </c>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Qashqadaryo, Yakkabog' tumani</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Yakkabog' tumani 69-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
+          <t>60201085720092</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>AE4328716</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>908785105</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>916397685</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>General Secondary School No. 69, Yakkabog District</t>
+          <t>Shahrisabz shahri 36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Maktab</t>
+          <t>General Secondary School No. 36, Shahrisabz City</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>UM 03758009</t>
+          <t>Maktab</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>UM 03718337</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -2259,52 +2420,55 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>62508085680062</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>AE2656510</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>881708081</v>
+          <t>62511085730064</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>AE4729924</t>
+        </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>880410227</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Qashqadaryo, Kitob tumani</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Kitob tumani 12-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
+        <v>997422473</v>
+      </c>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Yakkabog' tumani</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>General Secondary School No. 12, Kitob District</t>
+          <t>Yakkabog' tumani 69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Maktab</t>
+          <t>General Secondary School No. 69, Yakkabog District</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>UM 03728374</t>
+          <t>Maktab</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>UM 03758009</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -2316,52 +2480,119 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>62508085680062</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>AE2656510</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>881708081</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>880410227</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Kitob tumani</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Kitob tumani 12-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>General Secondary School No. 12, Kitob District</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>UM 03728374</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2015-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
           <t>Xurramova Sabina Yuldosh qizi</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>60803048230011</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>AC3081523</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="F37" s="2" t="n">
         <v>979602535</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>912162304</v>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 4-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 4, Yakkabog District</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>UM 1315230</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>2011-2022</t>
         </is>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-03).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-03).xlsx
@@ -609,15 +609,21 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>940790106</v>
-      </c>
-      <c r="G5" s="2" t="n"/>
+        <v>407901060</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>351375740</v>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n"/>
+          <t>Qashqadaryo, Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Galabek MFY, Maftunkor koʻchasi, 39-uy</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 50-sonli umumiy o'rta ta'lim maktabi</t>
@@ -729,15 +735,21 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
+        <v>705180560</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>997307709</v>
       </c>
-      <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Kattabogʻ MFY, Mardona koʻchasi, 56-uy</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 43-sonli umumiy o'rta ta'lim maktabi</t>
@@ -913,17 +925,21 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>999430596</v>
+        <v>593992050</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>959399205</v>
+        <v>523327660</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Gelon MFY, Gelon, 43uy</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 58-sonli umumiy o'rta ta'lim maktabi</t>
@@ -975,15 +991,21 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
+        <v>45042400</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>939034744</v>
       </c>
-      <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Kitob tumani</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n"/>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Alaquyliq MFY, Mevali koʻchasi, 85-uy</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 20-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1213,17 +1235,21 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
+        <v>780066370</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>970012780</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>973157721</v>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Yangibogʻ MFY, Mirzo Ulugʻbek koʼchasi, 41-uy</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 19-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1278,14 +1304,18 @@
         <v>772131924</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>919584082</v>
+        <v>548408291</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Hisorak MFY, Duoba qishlog'i, 1 - uy</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1344,10 +1374,14 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Oq Oltin MFY, Al-Xorazmiy koʼchasi, 212-uy</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 68-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1461,7 +1495,7 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>503019503</v>
+        <v>501582729</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>997304804</v>
@@ -1471,7 +1505,11 @@
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Turon MFY, Turon koʻchasi, 52.0</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 49-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1523,15 +1561,21 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>919595774</v>
-      </c>
-      <c r="G20" s="2" t="n"/>
+        <v>195957710</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>919595771</v>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Oq oltin MFY, Mehnatsevar kòchasi, 39-uy</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 68-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1583,7 +1627,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>880632608</v>
+        <v>806326080</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>973360140</v>
@@ -1593,7 +1637,11 @@
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Charmgar MFY, Nomozgoh ko'chasi, 124-uy</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 4-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1765,17 +1813,21 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>330578323</v>
+        <v>47809270</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>334248323</v>
+        <v>305783230</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Obod MFY, Qushboshi, 6-uy</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 38-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1827,7 +1879,7 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>885020703</v>
+        <v>850207030</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>880037679</v>
@@ -1837,7 +1889,11 @@
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Chagʼatoy, Yuq, 76.0</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 69-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1891,13 +1947,19 @@
       <c r="F26" s="2" t="n">
         <v>704785808</v>
       </c>
-      <c r="G26" s="2" t="n"/>
+      <c r="G26" s="2" t="n">
+        <v>887538486</v>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Kitob tumani</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Sanam MFY, Uzumzor kochasi, 60.0</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-son texnikumi</t>
@@ -1949,15 +2011,21 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>955838858</v>
-      </c>
-      <c r="G27" s="2" t="n"/>
+        <v>558388580</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>916417532</v>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Hisorak MFY, Chungurak qishloği, 132-uy</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2009,17 +2077,21 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
+        <v>874853608</v>
+      </c>
+      <c r="G28" s="2" t="n">
         <v>971880757</v>
       </c>
-      <c r="G28" s="2" t="n">
-        <v>973810757</v>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Bog'ishamol MFY, Sa‘d Ibn vaqqos ko‘chasi, 33 -uy</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 26-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2071,15 +2143,21 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>887611310</v>
-      </c>
-      <c r="G29" s="2" t="n"/>
+        <v>876113100</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>738982040</v>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Рус кишлак МФЮ, Улица Рус кишлак, Дом-11</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 25-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2200,10 +2278,14 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Kitob tumani</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n"/>
+          <t>Qashqadaryo, Китоб</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>китоб МФЯ, гулустон кучаси, 90.0</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 12-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2255,17 +2337,21 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>888659008</v>
+        <v>898183800</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>881861712</v>
+        <v>883861712</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Bogʻishamol MFY, Qorapoycha, 6 uy</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 26-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2317,15 +2403,21 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>772254208</v>
-      </c>
-      <c r="G33" s="2" t="n"/>
+        <v>722542080</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>994513820</v>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Sanam MFY, Shahrisabz koʻchasi, 163-uy</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-son texnikumi</t>
@@ -2377,17 +2469,21 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>908785105</v>
+        <v>862338080</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>916397685</v>
+        <v>770216705</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n"/>
+          <t>Qashqadaryo, Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Qirgʻiz MFY, Ming terak koʻchasi, 20-uy</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 36-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2439,15 +2535,21 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>997422473</v>
-      </c>
-      <c r="G35" s="2" t="n"/>
+        <v>514708250</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>224730951</v>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Kenguzar MFY, Chig'atoy, 6.0</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 69-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2499,17 +2601,21 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>881708081</v>
+        <v>804102270</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>880410227</v>
+        <v>817080810</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Xoji MFY, Uzunqir kuchasi, 106.0</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 12-sonli umumiy o'rta ta'lim maktabi</t>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-03).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-03).xlsx
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>407901060</v>
+        <v>940790106</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>351375740</v>
+        <v>935137574</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -677,13 +677,19 @@
       <c r="F6" s="2" t="n">
         <v>917090876</v>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="2" t="n">
+        <v>918127697</v>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Yakkabog' tumani</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n"/>
+          <t>Qashqadaryo, Yakkabogʻ tumani</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Tatar MFY, Yangi hayot koʻchasi, 49_uy</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 25-sonli umumiy o'rta ta'lim maktabi</t>
@@ -742,7 +748,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Yakkabog' tumani</t>
+          <t>Qashqadaryo, Yakkabogʻ tumani</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -925,14 +931,14 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>593992050</v>
+        <v>959399205</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>523327660</v>
+        <v>952332766</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -991,14 +997,14 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45042400</v>
+        <v>504504240</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>939034744</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Qashqadaryo, Qashqadaryo tumani</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1235,14 +1241,14 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>780066370</v>
+        <v>878006637</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>970012780</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1304,11 +1310,11 @@
         <v>772131924</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>548408291</v>
+        <v>915484082</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1374,12 +1380,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Oq Oltin MFY, Al-Xorazmiy koʼchasi, 212-uy</t>
+          <t>Oq Oltin MFY, Al- Xorazmiy, 212-uy</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1502,12 +1508,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrizabz tumani</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Turon MFY, Turon koʻchasi, 52.0</t>
+          <t>Turon MFY, Turon koʻchasi, 52-uy</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1561,14 +1567,14 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>195957710</v>
+        <v>919595771</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>919595771</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1627,7 +1633,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>806326080</v>
+        <v>880632608</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>973360140</v>
@@ -1761,7 +1767,11 @@
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Bunyodkor, Alpomish, 13-uy</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 7-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1813,10 +1823,10 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>47809270</v>
+        <v>704780927</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>305783230</v>
+        <v>330578323</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1879,19 +1889,19 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>850207030</v>
+        <v>885020703</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>880037679</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Yakkabog' tumani</t>
+          <t>Qashqadaryo, Yakkabogʼ</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Chagʼatoy, Yuq, 76.0</t>
+          <t>Chagʼatoy, Yuq, 76-uy</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1952,12 +1962,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabiz tumani</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Sanam MFY, Uzumzor kochasi, 60.0</t>
+          <t>Sanam MFY, Uzumzor kochasi, 60-uy</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2011,14 +2021,14 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>558388580</v>
+        <v>955838858</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>916417532</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2084,7 +2094,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2143,14 +2153,14 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>876113100</v>
+        <v>887611310</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>738982040</v>
+        <v>973898204</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Kitob tumani</t>
+          <t>Qashqadaryo, Китабский район</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2278,12 +2288,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Китоб</t>
+          <t>Qashqadaryo, китоб</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>китоб МФЯ, гулустон кучаси, 90.0</t>
+          <t>китоб МФЯ, гулустон кучаси, 90-uy</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2337,14 +2347,14 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>898183800</v>
+        <v>889818380</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>883861712</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2403,10 +2413,10 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>722542080</v>
+        <v>772254208</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>994513820</v>
+        <v>999451382</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2469,7 +2479,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>862338080</v>
+        <v>886233808</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>770216705</v>
@@ -2535,19 +2545,19 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>514708250</v>
+        <v>951470825</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>224730951</v>
+        <v>997422473</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Yakkabog' tumani</t>
+          <t>Qashqadaryo, Yakkabog'</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Kenguzar MFY, Chig'atoy, 6.0</t>
+          <t>Kenguzar MFY, Chig'atoy, 6-uy</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2601,10 +2611,10 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>804102270</v>
+        <v>880410227</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>817080810</v>
+        <v>881708081</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2613,7 +2623,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Xoji MFY, Uzunqir kuchasi, 106.0</t>
+          <t>Xoji MFY, Uzunqir kuchasi, 106-uy</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-03).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-03).xlsx
@@ -1182,14 +1182,22 @@
           <t>AB9205278</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
+      <c r="F14" s="2" t="n">
+        <v>992174752</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>955284081</v>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Alaqo'yliq MFY, Mevali ko'chasi, 109-uy</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
